--- a/output/pdf_financials_xlsx/CRWN.xlsx
+++ b/output/pdf_financials_xlsx/CRWN.xlsx
@@ -4473,10 +4473,10 @@
         <v>0</v>
       </c>
       <c r="I106" s="3" t="n">
-        <v>0</v>
+        <v>0.035</v>
       </c>
       <c r="J106" s="3" t="n">
-        <v>0</v>
+        <v>0.097</v>
       </c>
     </row>
     <row r="107">
@@ -8471,7 +8471,11 @@
           <t>Translation reserve</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E42" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/CRWN.xlsx
+++ b/output/pdf_financials_xlsx/CRWN.xlsx
@@ -521,45 +521,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C4" s="3" t="n">
+        <v>2.511715</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>11.51</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>20.311</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>26.592</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>28.252</v>
       </c>
       <c r="H4" s="1" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I4" s="3" t="n">
+        <v>1.593</v>
+      </c>
+      <c r="J4" s="3" t="n">
+        <v>2.132</v>
       </c>
     </row>
     <row r="5">
@@ -3600,13 +3586,13 @@
         <v>0</v>
       </c>
       <c r="H82" s="3" t="n">
-        <v>0</v>
+        <v>1.282</v>
       </c>
       <c r="I82" s="3" t="n">
-        <v>0</v>
+        <v>3.552</v>
       </c>
       <c r="J82" s="3" t="n">
-        <v>0</v>
+        <v>3.839</v>
       </c>
     </row>
     <row r="83">
@@ -3634,13 +3620,13 @@
         <v>0</v>
       </c>
       <c r="H83" s="3" t="n">
-        <v>0</v>
+        <v>1.282</v>
       </c>
       <c r="I83" s="3" t="n">
-        <v>0.06</v>
+        <v>3.612</v>
       </c>
       <c r="J83" s="3" t="n">
-        <v>0.011</v>
+        <v>3.85</v>
       </c>
     </row>
     <row r="84">
@@ -3770,13 +3756,13 @@
         <v>0</v>
       </c>
       <c r="H87" s="3" t="n">
-        <v>16.297</v>
+        <v>15.015</v>
       </c>
       <c r="I87" s="3" t="n">
-        <v>37.421</v>
+        <v>33.869</v>
       </c>
       <c r="J87" s="3" t="n">
-        <v>57.269</v>
+        <v>53.43</v>
       </c>
     </row>
     <row r="88">
@@ -3876,13 +3862,13 @@
         <v>0</v>
       </c>
       <c r="H90" s="3" t="n">
-        <v>0</v>
+        <v>0.644</v>
       </c>
       <c r="I90" s="3" t="n">
-        <v>0</v>
+        <v>16.753</v>
       </c>
       <c r="J90" s="3" t="n">
-        <v>0</v>
+        <v>15.302</v>
       </c>
     </row>
     <row r="91">
@@ -3910,13 +3896,13 @@
         <v>0</v>
       </c>
       <c r="H91" s="3" t="n">
-        <v>-0.184</v>
+        <v>0.46</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>20.991</v>
+        <v>37.744</v>
       </c>
       <c r="J91" s="3" t="n">
-        <v>2.353</v>
+        <v>17.655</v>
       </c>
     </row>
     <row r="92">
@@ -3954,13 +3940,13 @@
         </is>
       </c>
       <c r="H92" s="3" t="n">
-        <v>-0.002663771263119797</v>
+        <v>0.025218964893232</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0.4154529307282416</v>
+        <v>0.8161831458456681</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0.0618394893795124</v>
+        <v>0.5625457779637961</v>
       </c>
     </row>
     <row r="93">
@@ -4262,13 +4248,13 @@
         <v>0</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>46.765</v>
+        <v>46.121</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>44.369</v>
+        <v>27.616</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>52.933</v>
+        <v>37.631</v>
       </c>
     </row>
     <row r="101">
@@ -4709,7 +4695,7 @@
         <v>18.071</v>
       </c>
       <c r="F114" s="3" t="n">
-        <v>20.276</v>
+        <v>7.051</v>
       </c>
       <c r="G114" s="3" t="n">
         <v>-0.209</v>
@@ -5455,25 +5441,25 @@
         <v>0</v>
       </c>
       <c r="D136" s="3" t="n">
-        <v>0</v>
+        <v>-0.146</v>
       </c>
       <c r="E136" s="3" t="n">
-        <v>0</v>
+        <v>-0.422</v>
       </c>
       <c r="F136" s="3" t="n">
-        <v>0</v>
+        <v>-1.3</v>
       </c>
       <c r="G136" s="3" t="n">
-        <v>0</v>
+        <v>-1.811</v>
       </c>
       <c r="H136" s="3" t="n">
-        <v>0</v>
+        <v>-13.804</v>
       </c>
       <c r="I136" s="3" t="n">
-        <v>0</v>
+        <v>-10.969</v>
       </c>
       <c r="J136" s="3" t="n">
-        <v>0</v>
+        <v>-0.413</v>
       </c>
     </row>
     <row r="137">
@@ -7464,7 +7450,11 @@
           <t>Current portion of lease obligations</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
           <t>-</t>
@@ -7828,7 +7818,11 @@
           <t>Lease obligations</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LongTermCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E31" t="inlineStr">
         <is>
           <t>-</t>
@@ -16125,7 +16119,11 @@
           <t>Deferred tax expense (recovery)</t>
         </is>
       </c>
-      <c r="D172" t="inlineStr"/>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E172" t="inlineStr">
         <is>
           <t>-</t>
@@ -17749,7 +17747,11 @@
           <t>Shares repurchased (Note 22)</t>
         </is>
       </c>
-      <c r="D200" t="inlineStr"/>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E200" t="inlineStr">
         <is>
           <t>-</t>
@@ -18895,7 +18897,11 @@
           <t>Deferred tax recovery</t>
         </is>
       </c>
-      <c r="D220" t="inlineStr"/>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E220" t="inlineStr">
         <is>
           <t>-</t>
@@ -19965,7 +19971,11 @@
           <t>Shares repurchased (Note 20)</t>
         </is>
       </c>
-      <c r="D238" t="inlineStr"/>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E238" t="inlineStr">
         <is>
           <t>-</t>
@@ -20144,7 +20154,11 @@
           <t>Net income (loss) $</t>
         </is>
       </c>
-      <c r="D241" t="inlineStr"/>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E241" t="inlineStr">
         <is>
           <t>-</t>
@@ -21389,7 +21403,11 @@
           <t>Shares repurchased (Note 6)</t>
         </is>
       </c>
-      <c r="D262" t="inlineStr"/>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E262" t="inlineStr">
         <is>
           <t>-</t>
@@ -23360,7 +23378,11 @@
           <t>Shares repurchased (Note 7)</t>
         </is>
       </c>
-      <c r="D295" t="inlineStr"/>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E295" t="inlineStr">
         <is>
           <t>-</t>
@@ -25727,7 +25749,11 @@
           <t>Distributed power interest revenue</t>
         </is>
       </c>
-      <c r="D334" t="inlineStr"/>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>InterestIncome</t>
+        </is>
+      </c>
       <c r="E334" t="inlineStr">
         <is>
           <t>-</t>
@@ -27885,7 +27911,11 @@
           <t>Interest revenue $</t>
         </is>
       </c>
-      <c r="D370" t="inlineStr"/>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>InterestIncome</t>
+        </is>
+      </c>
       <c r="E370" t="inlineStr">
         <is>
           <t>-</t>
@@ -30502,7 +30532,11 @@
           <t>Interest revenue</t>
         </is>
       </c>
-      <c r="D415" t="inlineStr"/>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>InterestIncome</t>
+        </is>
+      </c>
       <c r="E415" t="inlineStr">
         <is>
           <t>-</t>
